--- a/artfynd/A 58238-2021 artfynd.xlsx
+++ b/artfynd/A 58238-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58238-2021 artfynd.xlsx
+++ b/artfynd/A 58238-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>349537</v>
+        <v>93486</v>
       </c>
       <c r="B2" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406731.2885934571</v>
+        <v>406731</v>
       </c>
       <c r="R2" t="n">
-        <v>7084523.711546343</v>
+        <v>7084480</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>93486</v>
+        <v>349537</v>
       </c>
       <c r="B3" t="n">
-        <v>89576</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406730.8595821456</v>
+        <v>406731</v>
       </c>
       <c r="R3" t="n">
-        <v>7084479.623370584</v>
+        <v>7084524</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>402521</v>
+        <v>357872</v>
       </c>
       <c r="B4" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406529.6382940447</v>
+        <v>406661</v>
       </c>
       <c r="R4" t="n">
-        <v>7084736.104434595</v>
+        <v>7084547</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +981,7 @@
         <v>402520</v>
       </c>
       <c r="B5" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406736.9576753401</v>
+        <v>406737</v>
       </c>
       <c r="R5" t="n">
-        <v>7084476.795805914</v>
+        <v>7084477</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>437957</v>
+        <v>402521</v>
       </c>
       <c r="B6" t="n">
-        <v>73697</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406718.031357563</v>
+        <v>406530</v>
       </c>
       <c r="R6" t="n">
-        <v>7084538.218321842</v>
+        <v>7084736</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,21 +1147,11 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1235,14 +1160,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>2 substratenheter</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1266,12 +1183,7 @@
         <v>437956</v>
       </c>
       <c r="B7" t="n">
-        <v>73697</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406774.8614186606</v>
+        <v>406775</v>
       </c>
       <c r="R7" t="n">
-        <v>7084474.344961933</v>
+        <v>7084474</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,19 +1248,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>357872</v>
+        <v>437957</v>
       </c>
       <c r="B8" t="n">
-        <v>77667</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406661.3147481457</v>
+        <v>406718</v>
       </c>
       <c r="R8" t="n">
-        <v>7084546.522199104</v>
+        <v>7084538</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1452,21 +1349,11 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1475,6 +1362,14 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>2 substratenheter</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 58238-2021 artfynd.xlsx
+++ b/artfynd/A 58238-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93486</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/349537</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/357872</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/402520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/402521</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/437956</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,8 +1422,22 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/437957</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>